--- a/ci-cd-merge-resolver/repoCollector/datasets/linkis.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/linkis.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -60,24 +60,6 @@
   </si>
   <si>
     <t>1d675778779a8319fba1cd2b11ea1a47d99e7e0f</t>
-  </si>
-  <si>
-    <t>1439f4dc6bcbe56e0d42eeef2a708240fbd37375</t>
-  </si>
-  <si>
-    <t>af0eb02f1f75e47d2148648e1fb9b4c66cde4fa4</t>
-  </si>
-  <si>
-    <t>55da24ab154c250a82c1bb4b64a2defe80f0bdbe</t>
-  </si>
-  <si>
-    <t>72ba5b54209d686822b0fdfaf66fba5d25637221</t>
-  </si>
-  <si>
-    <t>777fe600a86e2482acccd5d0e5d0056fa1a8caff</t>
-  </si>
-  <si>
-    <t>584ea70b2290bcf92afdc92f64ec9b2f6b0ab9d5</t>
   </si>
 </sst>
 </file>
@@ -122,7 +104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -183,10 +165,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>2.8519997596740723</v>
+        <v>0.4000000059604645</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -215,74 +197,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>2.19599986076355</v>
+        <v>0.25999999046325684</v>
       </c>
       <c r="J3" t="b" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="D4" t="n" s="0">
-        <v>100.0</v>
-      </c>
-      <c r="E4" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="F4" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="G4" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="H4" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n" s="0">
-        <v>7.673999309539795</v>
-      </c>
-      <c r="J4" t="b" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="D5" t="n" s="0">
-        <v>89.0</v>
-      </c>
-      <c r="E5" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="F5" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G5" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="H5" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n" s="0">
-        <v>3.7039999961853027</v>
-      </c>
-      <c r="J5" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
